--- a/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
+++ b/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
@@ -826,14 +826,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45163.60854391352</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -855,8 +851,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="15">
       <c r="A11" s="18" t="inlineStr">
         <is>
@@ -925,7 +919,7 @@
       </c>
       <c r="C30" s="21" t="n"/>
       <c r="D30" s="16" t="n">
-        <v>311.37</v>
+        <v>338</v>
       </c>
       <c r="E30" s="3" t="n"/>
     </row>
@@ -942,14 +936,13 @@
       </c>
       <c r="C31" s="21" t="n"/>
       <c r="D31" s="8" t="n">
-        <v>375.57</v>
+        <v>405</v>
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="15">
       <c r="E32" s="3" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="15">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -958,12 +951,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
+++ b/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
@@ -951,13 +951,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
+++ b/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
@@ -826,7 +826,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
@@ -951,13 +951,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
+++ b/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
@@ -826,7 +826,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
+++ b/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
@@ -826,7 +826,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
+++ b/LISTAS/ma/CAJAS PARA ENRROLLADOR.xlsx
@@ -826,10 +826,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45266</v>
+        <v>45225.50783299423</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -851,6 +855,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="15">
       <c r="A11" s="18" t="inlineStr">
         <is>
@@ -919,7 +925,7 @@
       </c>
       <c r="C30" s="21" t="n"/>
       <c r="D30" s="16" t="n">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="E30" s="3" t="n"/>
     </row>
@@ -936,13 +942,14 @@
       </c>
       <c r="C31" s="21" t="n"/>
       <c r="D31" s="8" t="n">
-        <v>405</v>
+        <v>454</v>
       </c>
       <c r="E31" s="3" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="15">
       <c r="E32" s="3" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="15">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -951,12 +958,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
